--- a/data/trans_dic/IP31KM13_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM13_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>99,41%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>97,12; 100,0</t>
+          <t>89,91; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>89,64; 100,0</t>
+          <t>96,98; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94,46; 99,71</t>
+          <t>93,69; 99,71</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,16; 90,97</t>
+          <t>73,15; 87,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,29; 87,07</t>
+          <t>68,98; 84,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74,31; 86,7</t>
+          <t>73,92; 83,98</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,93; 95,35</t>
+          <t>95,02; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>93,97; 100,0</t>
+          <t>81,19; 95,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,77; 96,97</t>
+          <t>89,77; 97,02</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,64; 98,79</t>
+          <t>50,1; 94,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,54; 95,6</t>
+          <t>88,96; 98,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,05; 95,54</t>
+          <t>69,48; 95,83</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>90,9; 100,0</t>
+          <t>92,46; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92,83; 100,0</t>
+          <t>89,14; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,08; 99,4</t>
+          <t>93,99; 99,36</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>91,87; 100,0</t>
+          <t>90,8; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92,36; 100,0</t>
+          <t>91,93; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,88; 99,3</t>
+          <t>93,86; 99,34</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,9; 96,51</t>
+          <t>88,64; 95,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>88,95; 96,4</t>
+          <t>88,49; 96,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90,37; 95,79</t>
+          <t>90,22; 95,3</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>91,06; 97,38</t>
+          <t>88,5; 96,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>89,01; 96,39</t>
+          <t>91,23; 97,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91,4; 96,25</t>
+          <t>91,31; 96,3</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>89,8; 93,96</t>
+          <t>86,75; 93,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>85,79; 93,42</t>
+          <t>90,18; 93,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89,21; 93,17</t>
+          <t>89,57; 93,07</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>70980</t>
+          <t>58385</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72446</t>
+          <t>54600</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143425</t>
+          <t>112987</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69341; 71400</t>
+          <t>54185; 60263</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>66879; 74607</t>
+          <t>53264; 54922</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>137915; 145587</t>
+          <t>107923; 114856</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>110</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>101274</t>
+          <t>93072</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>102061</t>
+          <t>76920</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203334</t>
+          <t>169992</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89411; 114307</t>
+          <t>84086; 100494</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92660; 110072</t>
+          <t>68519; 83658</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>187316; 218554</t>
+          <t>158401; 179958</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49581</t>
+          <t>56389</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63535</t>
+          <t>48322</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113115</t>
+          <t>104711</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45514; 52970</t>
+          <t>54446; 57299</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60736; 64633</t>
+          <t>43935; 51470</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107893; 116546</t>
+          <t>100016; 108091</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>66562</t>
+          <t>56434</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>60260</t>
+          <t>67223</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126822</t>
+          <t>123657</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62463; 68841</t>
+          <t>34978; 66063</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33566; 72053</t>
+          <t>62679; 69610</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90000; 138580</t>
+          <t>97464; 134424</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33214</t>
+          <t>38993</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40141</t>
+          <t>34339</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73355</t>
+          <t>73332</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31089; 34200</t>
+          <t>36593; 39579</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37800; 40719</t>
+          <t>31529; 35370</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70485; 74473</t>
+          <t>70447; 74468</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>72</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>43228</t>
+          <t>46008</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52460</t>
+          <t>43161</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95688</t>
+          <t>89169</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40690; 44290</t>
+          <t>42866; 47209</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49673; 53782</t>
+          <t>40714; 44286</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92069; 97389</t>
+          <t>85874; 90889</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>163</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>115902</t>
+          <t>130562</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>144426</t>
+          <t>113660</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>260328</t>
+          <t>244223</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>109965; 119376</t>
+          <t>124597; 134728</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>137908; 149461</t>
+          <t>107798; 117703</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>251892; 266996</t>
+          <t>236741; 250062</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>174</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>122413</t>
+          <t>146168</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>143866</t>
+          <t>131578</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>266277</t>
+          <t>277746</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>117168; 125292</t>
+          <t>139069; 151081</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>137223; 148600</t>
+          <t>125803; 134776</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>258502; 272216</t>
+          <t>269409; 284125</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>846</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>603153</t>
+          <t>626011</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>679193</t>
+          <t>569803</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1282346</t>
+          <t>1195814</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>586492; 613665</t>
+          <t>595829; 640733</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>638897; 695737</t>
+          <t>557527; 579751</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1247065; 1302456</t>
+          <t>1168873; 1214604</t>
         </is>
       </c>
     </row>
